--- a/artfynd/A 3204-2024 artfynd.xlsx
+++ b/artfynd/A 3204-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120519627</v>
+        <v>120518775</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534412</v>
+        <v>534222</v>
       </c>
       <c r="R3" t="n">
-        <v>6743944</v>
+        <v>6743877</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120518775</v>
+        <v>120518878</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>74593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öratjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534222</v>
+        <v>534266</v>
       </c>
       <c r="R4" t="n">
-        <v>6743877</v>
+        <v>6743845</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +960,18 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på klena granar i sumpskog</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120518878</v>
+        <v>120519627</v>
       </c>
       <c r="B5" t="n">
-        <v>74593</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öratjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534266</v>
+        <v>534412</v>
       </c>
       <c r="R5" t="n">
-        <v>6743845</v>
+        <v>6743944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,18 +1068,12 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt på klena granar i sumpskog</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3204-2024 artfynd.xlsx
+++ b/artfynd/A 3204-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120519918</v>
+        <v>120518775</v>
       </c>
       <c r="B2" t="n">
-        <v>79527</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534335</v>
+        <v>534222</v>
       </c>
       <c r="R2" t="n">
-        <v>6743994</v>
+        <v>6743877</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120518775</v>
+        <v>120519918</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>79527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534222</v>
+        <v>534335</v>
       </c>
       <c r="R3" t="n">
-        <v>6743877</v>
+        <v>6743994</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 3204-2024 artfynd.xlsx
+++ b/artfynd/A 3204-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120518878</v>
+        <v>120519725</v>
       </c>
       <c r="B2" t="n">
-        <v>74641</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öratjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534266</v>
+        <v>534434</v>
       </c>
       <c r="R2" t="n">
-        <v>6743845</v>
+        <v>6744010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,18 +748,12 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt på klena granar i sumpskog</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120519627</v>
+        <v>120520045</v>
       </c>
       <c r="B3" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534412</v>
+        <v>534283</v>
       </c>
       <c r="R3" t="n">
-        <v>6743944</v>
+        <v>6744000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,16 +872,11 @@
         <v>120518775</v>
       </c>
       <c r="B4" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -990,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120519918</v>
+        <v>120519203</v>
       </c>
       <c r="B5" t="n">
-        <v>79579</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534335</v>
+        <v>534278</v>
       </c>
       <c r="R5" t="n">
-        <v>6743994</v>
+        <v>6743818</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,6 +1060,694 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120519627</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öratjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>534412</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6743944</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120519734</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öratjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>534434</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6744010</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120518878</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öratjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>534266</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6743845</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt på klena granar i sumpskog</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120518966</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öratjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>534281</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6743828</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120519187</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öratjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>534278</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6743818</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120519120</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öratjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>534281</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6743828</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120519918</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öratjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>534335</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6743994</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3204-2024 artfynd.xlsx
+++ b/artfynd/A 3204-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120520045</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120518775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519203</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519627</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519734</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120518878</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120518966</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519187</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519120</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,8 +1803,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120519918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>